--- a/plantillas/curriculum2.xlsx
+++ b/plantillas/curriculum2.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28730"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Isac\Documents\Formulario Servicio\formulario-servicio\plantillas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\source\repos\NodeJS\PlataformaRecursosHumanos\plantillas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{513329E2-CA5A-4E7F-9749-0736386B9CB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="715" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="715"/>
   </bookViews>
   <sheets>
     <sheet name="FORMATO CURRICULUM TRANSPARENCI" sheetId="10" r:id="rId1"/>
@@ -64,9 +63,6 @@
     <t>CAMPO DE EXPERIENCIA</t>
   </si>
   <si>
-    <t>FECHA DE OBTENCIÓN DE GRADO              (MES / AÑO)</t>
-  </si>
-  <si>
     <t>INSTITUCIÓN QUE EXPIDIO EL TITULO</t>
   </si>
   <si>
@@ -113,12 +109,15 @@
   </si>
   <si>
     <t>.</t>
+  </si>
+  <si>
+    <t>FECHA DE OBTENCIÓN DE GRADO    (MES / AÑO)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -220,7 +219,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -247,17 +246,6 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right/>
       <top style="thin">
         <color indexed="64"/>
@@ -302,7 +290,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -359,25 +347,16 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -389,11 +368,35 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -524,9 +527,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -564,9 +567,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -601,7 +604,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -636,7 +639,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -809,7 +812,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Hoja1">
     <tabColor rgb="FFFFFF00"/>
     <pageSetUpPr fitToPage="1"/>
@@ -818,8 +821,8 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="12" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.28515625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="39.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="42.28515625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="51.85546875" style="2" customWidth="1"/>
     <col min="4" max="4" width="37.28515625" style="2" customWidth="1"/>
     <col min="5" max="5" width="21.7109375" style="2" customWidth="1"/>
     <col min="6" max="6" width="15.5703125" style="2" customWidth="1"/>
@@ -838,35 +841,35 @@
       <c r="G1" s="1"/>
     </row>
     <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.25">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
       <c r="F2" s="17"/>
       <c r="G2" s="17"/>
     </row>
     <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.25">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="23"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
       <c r="F3" s="17"/>
       <c r="G3" s="17"/>
     </row>
     <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.25">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
       <c r="F4" s="17"/>
       <c r="G4" s="17"/>
     </row>
@@ -880,13 +883,13 @@
       <c r="G5"/>
     </row>
     <row r="6" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6" s="27"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="27"/>
+      <c r="A6" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="24"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
       <c r="F6"/>
       <c r="G6"/>
     </row>
@@ -894,32 +897,32 @@
       <c r="A7" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="28"/>
-      <c r="C7" s="28"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="28"/>
+      <c r="B7" s="25"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
       <c r="F7"/>
       <c r="G7"/>
     </row>
     <row r="8" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="24"/>
-      <c r="C8" s="24"/>
-      <c r="D8" s="24"/>
-      <c r="E8" s="24"/>
+      <c r="A8" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="21"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
       <c r="F8"/>
       <c r="G8"/>
     </row>
     <row r="9" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="30" t="s">
+      <c r="A9" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9"/>
+      <c r="B9" s="28"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
       <c r="F9"/>
       <c r="G9"/>
     </row>
@@ -927,27 +930,27 @@
       <c r="A10" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="9" t="s">
+      <c r="B10" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="36" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10"/>
+      <c r="E10" s="31"/>
       <c r="F10"/>
       <c r="G10"/>
     </row>
     <row r="11" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="29"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="29"/>
-      <c r="E11"/>
+        <v>14</v>
+      </c>
+      <c r="B11" s="26"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="26"/>
       <c r="F11"/>
       <c r="G11"/>
     </row>
@@ -955,10 +958,10 @@
       <c r="A12" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="29"/>
-      <c r="C12" s="29"/>
-      <c r="D12" s="29"/>
-      <c r="E12"/>
+      <c r="B12" s="26"/>
+      <c r="C12" s="26"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="26"/>
       <c r="F12"/>
       <c r="G12"/>
     </row>
@@ -966,32 +969,32 @@
       <c r="A13" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="29"/>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29"/>
-      <c r="E13"/>
+      <c r="B13" s="26"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="26"/>
       <c r="F13"/>
       <c r="G13"/>
     </row>
     <row r="14" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="26"/>
       <c r="F14"/>
       <c r="G14"/>
     </row>
     <row r="15" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
       <c r="F15"/>
       <c r="G15"/>
     </row>
@@ -1001,8 +1004,8 @@
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="14"/>
-      <c r="D16" s="4"/>
-      <c r="E16"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
       <c r="F16"/>
       <c r="G16"/>
     </row>
@@ -1012,8 +1015,8 @@
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="14"/>
-      <c r="D17" s="4"/>
-      <c r="E17"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26"/>
       <c r="F17"/>
       <c r="G17"/>
     </row>
@@ -1023,46 +1026,47 @@
       </c>
       <c r="B18" s="12"/>
       <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="33"/>
       <c r="F18"/>
       <c r="G18"/>
     </row>
     <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="B19" s="24"/>
-      <c r="C19" s="24"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="24"/>
+      <c r="A19" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="21"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
       <c r="F19"/>
       <c r="G19"/>
     </row>
     <row r="20" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="B20" s="22"/>
-      <c r="C20" s="22"/>
-      <c r="D20" s="22"/>
-      <c r="E20"/>
+      <c r="A20" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="35"/>
+      <c r="C20" s="35"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="35"/>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
     </row>
     <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="C21" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>20</v>
-      </c>
+      <c r="E21" s="29"/>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
     </row>
@@ -1070,44 +1074,44 @@
       <c r="A22" s="5"/>
       <c r="B22" s="5"/>
       <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="1"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="26"/>
       <c r="F22" s="1"/>
     </row>
     <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="B23" s="25"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="25"/>
+      <c r="A23" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" s="22"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="22"/>
       <c r="F23" s="11"/>
       <c r="G23" s="6"/>
     </row>
     <row r="24" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="20" t="s">
+      <c r="A24" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="B24" s="20"/>
-      <c r="C24" s="20"/>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
+      <c r="B24" s="27"/>
+      <c r="C24" s="27"/>
+      <c r="D24" s="27"/>
+      <c r="E24" s="27"/>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
     </row>
     <row r="25" spans="1:7" ht="24" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="10" t="s">
-        <v>25</v>
-      </c>
       <c r="C25" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>12</v>
@@ -1330,24 +1334,32 @@
     <row r="231" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="232" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="22">
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="B13:E13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="A20:E20"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A8:E8"/>
     <mergeCell ref="A23:E23"/>
     <mergeCell ref="A19:E19"/>
     <mergeCell ref="A6:E6"/>
     <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D22:E22"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B11:B12" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B11:B12">
       <formula1>"SI,NO"</formula1>
     </dataValidation>
   </dataValidations>
